--- a/mapping/PDTD_DTM/Mapping_AGG_LOS_KPI_APPLICATION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_AGG_LOS_KPI_APPLICATION.xlsx
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -731,12 +731,7 @@
       </c>
       <c r="E1" s="52" t="inlineStr">
         <is>
-          <t>FCT_CLOS_APPLICATION AS A</t>
-        </is>
-      </c>
-      <c r="F1" s="52" t="inlineStr">
-        <is>
-          <t>FCT_RLOS_APPLICATION AS A</t>
+          <t>FCT_CLOS_APPLICATION AS A (nhánh CLOS, UNION ALL)</t>
         </is>
       </c>
     </row>
@@ -748,17 +743,12 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng tổng hợp chấm điểm KPI hồ sơ CLOS+RLOS (UNION ALL), full snapshot DAYID=v_batch_date, nguồn tính VOLUME/POINT/QUY_DOI cho AGG_LOS_KPI_YTD_DAILY</t>
+          <t>Bảng FACT chấm điểm KPI theo từng hồ sơ TẠI MỖI NGÀY — driving UNION ALL FCT_CLOS_APPLICATION + FCT_RLOS_APPLICATION (cả 2 tại PDTD_DTM), input pre-aggregate duy nhất cho AGG_LOS_KPI_YTD_DAILY</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
         <is>
-          <t>REF_SLA_NLTT AS C</t>
-        </is>
-      </c>
-      <c r="F2" s="52" t="inlineStr">
-        <is>
-          <t>REF_SLA_NLTT AS C</t>
+          <t>FCT_RLOS_APPLICATION AS B (nhánh RLOS, UNION ALL)</t>
         </is>
       </c>
     </row>
@@ -775,12 +765,7 @@
       </c>
       <c r="E3" s="52" t="inlineStr">
         <is>
-          <t>DIM_CLOS_PRODUCT PL AS E2</t>
-        </is>
-      </c>
-      <c r="F3" s="52" t="inlineStr">
-        <is>
-          <t>DIM_RLOS_PRODUCT AS D</t>
+          <t>REF_SLA_NLTT AS C</t>
         </is>
       </c>
     </row>
@@ -797,12 +782,7 @@
       </c>
       <c r="E4" s="52" t="inlineStr">
         <is>
-          <t>DIM_CLOS_PRODUCT SP AS F</t>
-        </is>
-      </c>
-      <c r="F4" s="52" t="inlineStr">
-        <is>
-          <t>STG_FCT_RLOS_COLLATERAL AS H</t>
+          <t>DIM_CLOS_PRODUCT AS PL/SP (layer Product Line/Sub Product, nhánh CLOS)</t>
         </is>
       </c>
     </row>
@@ -810,12 +790,7 @@
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>STG_DIM_CLOS_APPLICATION AS G</t>
-        </is>
-      </c>
-      <c r="F5" s="52" t="inlineStr">
-        <is>
-          <t>STG_DIM_RLOS_APPLICATION AS I</t>
+          <t>DIM_RLOS_PRODUCT AS D</t>
         </is>
       </c>
     </row>
@@ -823,12 +798,7 @@
       <c r="A6" s="13" t="n"/>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>STG_FCT_CLOS_DEVIATION AS J</t>
-        </is>
-      </c>
-      <c r="F6" s="52" t="inlineStr">
-        <is>
-          <t>STG_FCT_RLOS_DEVIATION AS K</t>
+          <t>STG_DIM_CLOS_APPLICATION AS E1</t>
         </is>
       </c>
     </row>
@@ -836,12 +806,7 @@
       <c r="A7" s="13" t="n"/>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>STG_FCT_CLOS_WORKSTEP_EVENT AS L</t>
-        </is>
-      </c>
-      <c r="F7" s="52" t="inlineStr">
-        <is>
-          <t>STG_FCT_RLOS_WORKSTEP_EVENT AS M</t>
+          <t>FCT_CLOS_WORKSTEP_EVENT AS F</t>
         </is>
       </c>
     </row>
@@ -849,44 +814,57 @@
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>FCT_CLOS_WORKSTEP_EVENT AS N</t>
-        </is>
-      </c>
-      <c r="F8" s="53" t="inlineStr">
-        <is>
-          <t>FCT_RLOS_WORKSTEP_EVENT AS O</t>
+          <t>FCT_RLOS_WORKSTEP_EVENT AS G</t>
         </is>
       </c>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
-      <c r="E9" s="53" t="n"/>
-      <c r="F9" s="52" t="n"/>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>STG_FCT_RLOS_COLLATERAL AS H</t>
+        </is>
+      </c>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
-      <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
+      <c r="E10" s="53" t="inlineStr">
+        <is>
+          <t>STG_DIM_RLOS_APPLICATION AS I</t>
+        </is>
+      </c>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
-      <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
+      <c r="E11" s="53" t="inlineStr">
+        <is>
+          <t>STG_FCT_CLOS_DEVIATION AS J</t>
+        </is>
+      </c>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
+      <c r="E12" s="53" t="inlineStr">
+        <is>
+          <t>STG_FCT_RLOS_DEVIATION AS K</t>
+        </is>
+      </c>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
-      <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
+      <c r="E13" s="53" t="inlineStr">
+        <is>
+          <t>STG_FCT_CLOS_WORKSTEP_EVENT AS L</t>
+        </is>
+      </c>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
-      <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
+      <c r="E14" s="53" t="inlineStr">
+        <is>
+          <t>STG_FCT_RLOS_WORKSTEP_EVENT AS M</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -912,11 +890,6 @@
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>How to mapping CLOS</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>How to mapping RLOS</t>
         </is>
       </c>
     </row>
@@ -930,7 +903,6 @@
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="12" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
@@ -950,21 +922,16 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Driving: UNION ALL CLOS + RLOS, full snapshot lọc DAYID=v_batch_date (KHÔNG lọc hồ sơ đã kết thúc). Ngày dữ liệu, dạng số YYYYMMDD</t>
+          <t>PK (1/2) — Driving: UNION ALL FCT_CLOS_APPLICATION + FCT_RLOS_APPLICATION, full snapshot lọc DAYID=v_batch_date (KHÔNG lọc hồ sơ đã kết thúc). Ngày dữ liệu, dạng số YYYYMMDD</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
         <is>
-          <t>A.DAYID WHERE A.DAYID = v_batch_date</t>
-        </is>
-      </c>
-      <c r="F17" s="31" t="inlineStr">
-        <is>
-          <t>A.DAYID WHERE A.DAYID = v_batch_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t>SELECT A.DAYID, A.WI_NAME FROM A WHERE A.DAYID = v_batch_date UNION ALL SELECT B.DAYID, B.WI_NAME FROM B WHERE B.DAYID = v_batch_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>DATASOURCE</t>
@@ -977,22 +944,17 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Hệ thống nguồn</t>
+          <t>Phân nhánh RLOS/CLOS</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>RLOS hoặc CLOS — quyết định công thức TAT/POINT/nhóm phân loại áp dụng. PDTD_DTM phân biệt hệ qua tên bảng riêng, không đọc cột DATASOURCE từ nguồn — gán literal theo đúng nhánh UNION ALL</t>
+          <t>RLOS hoặc CLOS — quyết định công thức TAT/POINT/nhóm phân loại áp dụng</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>'CLOS'</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>'RLOS'</t>
+          <t>'CLOS' AS DATASOURCE (literal, gán trong nhánh UNION ALL đọc từ A; nhánh RLOS gán literal 'RLOS' trong nhánh UNION ALL đọc từ B)</t>
         </is>
       </c>
     </row>
@@ -1009,7 +971,7 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ chấm điểm hồ sơ</t>
+          <t>Khóa nghiệp vụ dòng KPI</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
@@ -1019,16 +981,11 @@
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>STANDARD_HASH(A.WI_NAME || 'CLOS', 'MD5')</t>
-        </is>
-      </c>
-      <c r="F19" s="31" t="inlineStr">
-        <is>
-          <t>STANDARD_HASH(A.WI_NAME || 'RLOS', 'MD5')</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+          <t>STANDARD_HASH(WI_NAME || DATASOURCE, 'MD5')</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -1041,12 +998,12 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_APPLICATION hoặc DIM_RLOS_APPLICATION tùy DATASOURCE. Mặc định -1</t>
+          <t>Khóa tới DIM_CLOS_APPLICATION hoặc DIM_RLOS_APPLICATION tùy DATASOURCE. Nhánh RLOS lấy B.APPLICATION_SK trong cùng UNION ALL của dòng WI_NAME</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
@@ -1054,521 +1011,517 @@
           <t>A.APPLICATION_SK</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr">
-        <is>
-          <t>A.APPLICATION_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>PRODUCTLINE_SK</t>
+          <t>WI_NAME</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới nhóm sản phẩm</t>
+          <t>Mã hồ sơ</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>DATASOURCE=CLOS: khóa tới DIM_CLOS_PRODUCT (layer Product Line). DATASOURCE=RLOS: khóa tới DIM_RLOS_PRODUCT (layer Product Line). Mặc định -1</t>
+          <t>Mã hồ sơ tín dụng CLOS hoặc RLOS. Nhánh RLOS lấy B.WI_NAME trong cùng UNION ALL</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>A.PRODUCTLINE_SK</t>
-        </is>
-      </c>
-      <c r="F21" s="31" t="inlineStr">
-        <is>
-          <t>A.PRODUCTLINE_SK</t>
+          <t>A.WI_NAME</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
+          <t>PRODUCTLINE_SK</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Khóa dòng sản phẩm</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>DATASOURCE=CLOS: khóa tới DIM_CLOS_PRODUCT (layer Product Line). DATASOURCE=RLOS: khóa tới DIM_RLOS_PRODUCT (layer Product Line). Thay cho PRODUCT_SK cũ. Mặc định -1.</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE='CLOS' THEN A.PRODUCTLINE_SK ELSE B.PRODUCTLINE_SK END</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>PRODUCTLINE_CODE</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã dòng sản phẩm</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK (layer Product Line), giá trị đã có sẵn trên driving table trong bước lookup PRODUCTLINE_SK</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE='CLOS' THEN A.PRODUCTLINE_CODE ELSE B.PRODUCTLINE_CODE END</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
           <t>SUB_PRODUCT_SK</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới sản phẩm vay chi tiết</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>DATASOURCE=CLOS: khóa tới DIM_CLOS_PRODUCT (layer Sub Product). DATASOURCE=RLOS: khóa tới DIM_RLOS_PRODUCT (layer Sub Product, layer đại diện/grain chính). Mặc định -1</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>A.SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-      <c r="F22" s="31" t="inlineStr">
-        <is>
-          <t>A.SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>COMPANY_SK</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới công ty/tổ chức</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_COMPANY. Mặc định -1</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>A.COMPANY_SK</t>
-        </is>
-      </c>
-      <c r="F23" s="31" t="inlineStr">
-        <is>
-          <t>A.COMPANY_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>WI_NAME</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng</t>
+          <t>Khóa sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng CLOS hoặc RLOS</t>
+          <t>DATASOURCE=CLOS: khóa tới DIM_CLOS_PRODUCT (layer Sub Product). DATASOURCE=RLOS: khóa tới DIM_RLOS_PRODUCT (layer Sub Product, layer đại diện/grain chính). Nhánh RLOS gộp vào cột này. Mặc định -1.</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-      <c r="F24" s="31" t="inlineStr">
-        <is>
-          <t>A.WI_NAME</t>
+          <t>CASE WHEN DATASOURCE='CLOS' THEN A.SUB_PRODUCT_SK ELSE B.SUB_PRODUCT_SK END</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
+          <t>SUB_PRODUCT_CODE</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Mã sản phẩm nhánh</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK (layer Sub Product), giá trị đã có sẵn trên driving table trong bước lookup SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE='CLOS' THEN A.SUB_PRODUCT_CODE ELSE B.SUB_PRODUCT_CODE END</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>COMPANY_SK</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Khóa đơn vị kinh doanh</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_COMPANY. Mặc định -1. Nhánh RLOS lấy B.COMPANY_SK trong cùng UNION ALL của dòng WI_NAME.</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>A.COMPANY_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>COMPANY_CODE</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Mã đơn vị kinh doanh</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, cùng giá trị đã dùng để lookup COMPANY_SK</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE='CLOS' THEN A.COMPANY_CODE ELSE B.COMPANY_CODE END</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
           <t>PROCESSED_DATE</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Ngày xử lý</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Ngày xử lý của hồ sơ — mốc để AGG_LOS_KPI_YTD_DAILY xếp hồ sơ vào đúng DAYID khi SUM/COUNT lên grain ngày</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Ngày xử lý hồ sơ</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>Ngày xử lý của hồ sơ — mốc để AGG_LOS_KPI_YTD_DAILY xếp hồ sơ vào đúng DAYID khi SUM/COUNT lên grain ngày. Nhánh RLOS lấy B.PROCESSED_DATE trong cùng UNION ALL của dòng WI_NAME</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.PROCESSED_DATE</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr">
-        <is>
-          <t>A.PROCESSED_DATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="105" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
+    </row>
+    <row r="29" ht="240" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>VOLUME</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>NUMBER(5,2)</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>Mức độ hoàn thành hồ sơ</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>Mức độ hoàn thành hồ sơ, thang 0-1 — đọc 6 cờ trạng thái một-chiều trên FCT_CLOS/RLOS_APPLICATION (HAS_DDE/UWM/UWC/APPROVAL/FINAL_APPROVAL/CANCELLED_FLAG), JOIN qua PK WI_NAME+DAYID, O(1) lookup</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN A.HAS_FINAL_APPROVAL_FLAG = 'Y' THEN 1.0 WHEN A.HAS_CANCELLED_FLAG = 'Y' THEN CASE WHEN A.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN A.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN A.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN A.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END WHEN A.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN A.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN A.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN A.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END</t>
-        </is>
-      </c>
-      <c r="F26" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN A.HAS_FINAL_APPROVAL_FLAG = 'Y' THEN 1.0 WHEN A.HAS_CANCELLED_FLAG = 'Y' THEN CASE WHEN A.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN A.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN A.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN A.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END WHEN A.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN A.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN A.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN A.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="120" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Tỷ lệ KPI</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Mức độ hoàn thành hồ sơ, thang 0-1 — đọc trực tiếp 6 cờ trạng thái một-chiều trên FCT_CLOS/RLOS_APPLICATION (HAS_DDE/UWM/UWC/APPROVAL/FINAL_APPROVAL/CANCELLED_FLAG), JOIN qua PK WI_NAME+DAYID, O(1) lookup. (1) HAS_FINAL_APPROVAL_FLAG='Y' → 1.0; (2) HAS_CANCELLED_FLAG='Y' → điểm theo bước xa nhất đã đạt TRƯỚC KHI hủy; (3) còn lại → điểm theo bước xa nhất đã đạt, chưa tới DetailDataEntry → NULL.</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE = 'CLOS' THEN (SELECT CASE WHEN fa.HAS_FINAL_APPROVAL_FLAG = 'Y' THEN 1.0 WHEN fa.HAS_CANCELLED_FLAG = 'Y' THEN CASE WHEN fa.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN fa.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN fa.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN fa.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END WHEN fa.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN fa.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN fa.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN fa.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END FROM A fa WHERE fa.WI_NAME = WI_NAME AND fa.DAYID = DAYID) WHEN DATASOURCE = 'RLOS' THEN (SELECT CASE WHEN fa.HAS_FINAL_APPROVAL_FLAG = 'Y' THEN 1.0 WHEN fa.HAS_CANCELLED_FLAG = 'Y' THEN CASE WHEN fa.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN fa.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN fa.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN fa.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END WHEN fa.HAS_APPROVAL_FLAG = 'Y' THEN 0.8 WHEN fa.HAS_UWC_FLAG = 'Y' THEN 0.6 WHEN fa.HAS_UWM_FLAG = 'Y' THEN 0.5 WHEN fa.HAS_DDE_FLAG = 'Y' THEN 0.2 ELSE NULL END FROM B fa WHERE fa.WI_NAME = WI_NAME AND fa.DAYID = DAYID) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>POINT</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>NUMBER(12,4)</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>Điểm KPI</t>
         </is>
       </c>
-      <c r="D27" s="54" t="inlineStr">
-        <is>
-          <t>Điểm KPI — cam kết SLA nhập liệu tập trung + cam kết SLA phê duyệt tín dụng. SLA_DE_TOTAL_RESULT là report-time lookup (không denormalize vào DIM)</t>
-        </is>
-      </c>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>NVL((SELECT C.SLA_DE_TOTAL_RESULT FROM C JOIN E2 ON E2.PRODUCTLINE_SK = A.PRODUCTLINE_SK JOIN F ON F.SUB_PRODUCT_SK = A.SUB_PRODUCT_SK WHERE C.PRODUCT_LINE = E2.PRODUCTLINE_NAME AND (C.SUB_PRODUCT IS NULL OR C.SUB_PRODUCT = F.SUB_PRODUCT_NAME) AND C.NEW_CHANGE_REQUEST = A.CHANGE_REQUEST AND C.SYSTEM_CODE = 'CLOS'),0) + CASE WHEN (SELECT G.APP_GRP FROM G WHERE G.DIMENSION_KEY = A.APPLICATION_SK) = 'C1' THEN 4 ELSE NVL(A.SLA_CREDIT_OFFICER,0) + NVL(A.SLA_CREDIT_APPROVER,0) END</t>
-        </is>
-      </c>
-      <c r="F27" s="31" t="inlineStr">
-        <is>
-          <t>NVL((SELECT C.SLA_DE_TOTAL_RESULT FROM C JOIN D ON D.PRODUCTLINE_SK = A.PRODUCTLINE_SK WHERE C.PRODUCT_LINE = D.PRODUCTLINE_NAME AND C.SYSTEM_CODE = 'RLOS'),0) + NVL(A.SLA_CREDIT_OFFICER,0) + NVL(A.SLA_CREDIT_APPROVER,0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Điểm KPI — cam kết SLA nhập liệu tập trung + cam kết SLA phê duyệt tín dụng. Hồ sơ CLOS APP_GRP='C1': SLA_DE_TOTAL_RESULT + 4.00 (hằng số cứng, không cộng thêm SLA_CREDIT_OFFICER/APPROVER).</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE = 'RLOS' THEN NVL((SELECT C.SLA_DE_TOTAL_RESULT FROM C JOIN D ON D.PRODUCTLINE_SK = PRODUCTLINE_SK WHERE C.PRODUCT_LINE = D.PRODUCTLINE_NAME AND C.SYSTEM_CODE = 'RLOS'),0) + NVL((SELECT B.SLA_CREDIT_OFFICER FROM B WHERE B.WI_NAME = WI_NAME AND B.DAYID = DAYID),0) + NVL((SELECT B.SLA_CREDIT_APPROVER FROM B WHERE B.WI_NAME = WI_NAME AND B.DAYID = DAYID),0) WHEN DATASOURCE = 'CLOS' THEN NVL((SELECT C.SLA_DE_TOTAL_RESULT FROM C JOIN PL ON PL.PRODUCTLINE_SK = PRODUCTLINE_SK JOIN SP ON SP.SUB_PRODUCT_SK = SUB_PRODUCT_SK JOIN A ON A.WI_NAME = WI_NAME AND A.DAYID = DAYID WHERE C.PRODUCT_LINE = PL.PRODUCTLINE_NAME AND (C.SUB_PRODUCT IS NULL OR C.SUB_PRODUCT = SP.SUB_PRODUCT_NAME) AND C.NEW_CHANGE_REQUEST = A.CHANGE_REQUEST AND C.SYSTEM_CODE = 'CLOS'),0) + CASE WHEN (SELECT E1.APP_GRP FROM E1 JOIN A ON A.APPLICATION_SK = E1.DIMENSION_KEY WHERE A.WI_NAME = WI_NAME AND A.DAYID = DAYID) = 'C1' THEN 4 ELSE NVL((SELECT A.SLA_CREDIT_OFFICER FROM A WHERE A.WI_NAME = WI_NAME AND A.DAYID = DAYID),0) + NVL((SELECT A.SLA_CREDIT_APPROVER FROM A WHERE A.WI_NAME = WI_NAME AND A.DAYID = DAYID),0) END END</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>QUY_DOI</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>NUMBER(12,4)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Điểm KPI quy đổi</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
-        <is>
-          <t>Điểm KPI quy đổi. Nguyên văn SRS: Nếu VOLUME không NULL lấy POINT/(8*VOLUME) — có dấu ngoặc quanh (8*VOLUME). Là đầu vào duy nhất của QUY_DOI_RLOS/QUY_DOI_CLOS (tại-ngày) ở AGG_LOS_KPI_YTD_DAILY</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN AGG_LOS_KPI_APPLICATION.VOLUME IS NULL THEN NULL ELSE AGG_LOS_KPI_APPLICATION.POINT / (8 * AGG_LOS_KPI_APPLICATION.VOLUME) END</t>
-        </is>
-      </c>
-      <c r="F28" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN AGG_LOS_KPI_APPLICATION.VOLUME IS NULL THEN NULL ELSE AGG_LOS_KPI_APPLICATION.POINT / (8 * AGG_LOS_KPI_APPLICATION.VOLUME) END</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Điểm KPI quy đổi — POINT*8/VOLUME (input từ cột cùng bảng), NULL nếu VOLUME NULL. Là đầu vào duy nhất của QUY_DOI_RLOS/QUY_DOI_CLOS ở AGG_LOS_KPI_YTD_DAILY</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN VOLUME IS NULL THEN NULL ELSE POINT / (8 * VOLUME) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>TAT_APPLICATION_HOUR</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>NUMBER(18,6)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Tổng thời gian xử lý hồ sơ</t>
-        </is>
-      </c>
-      <c r="D29" s="54" t="inlineStr">
-        <is>
-          <t>Tổng thời gian xử lý của hồ sơ, đơn vị giờ. Bổ sung điều kiện APPROVAL_FLAG='First Approval' — loại trừ thời gian vòng làm lại (rework). CLOS cộng thêm CreditCommittee so với RLOS. Đọc từ chính PDTD_DTM.FCT_CLOS/RLOS_WORKSTEP_EVENT (TAT_WORKING_HOUR đã tính sẵn ở đó) — yêu cầu build trước AGG_LOS_KPI_APPLICATION trong thứ tự ETL</t>
-        </is>
-      </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT SUM(N.TAT_WORKING_HOUR) FROM N WHERE N.WI_NAME = A.WI_NAME AND N.WORKSTEP_CODE IN ('DetailDataEntry','DataInputerChecker','UnderwriterMaker','UnderwriterChecker','CreditApproval','CreditCommittee') AND N.APPROVAL_FLAG = 'First Approval')</t>
-        </is>
-      </c>
-      <c r="F29" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT SUM(O.TAT_WORKING_HOUR) FROM O WHERE O.WI_NAME = A.WI_NAME AND O.WORKSTEP_CODE IN ('DetailDataEntry','DataInputerChecker','UnderwriterMaker','UnderwriterChecker','CreditApproval') AND O.APPROVAL_FLAG = 'First Approval')</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Tổng thời gian xử lý</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Tổng thời gian xử lý của hồ sơ, đơn vị giờ. Bổ sung điều kiện APPROVAL_FLAG='First Approval' — loại trừ thời gian vòng làm lại. CLOS cộng thêm CreditCommittee so với RLOS.</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE = 'RLOS' THEN (SELECT SUM(G.TAT_WORKING_HOUR) FROM G WHERE G.WI_NAME = WI_NAME AND G.WORKSTEP_CODE IN ('DetailDataEntry','DataInputerChecker','UnderwriterMaker','UnderwriterChecker','CreditApproval') AND G.APPROVAL_FLAG = 'First Approval') WHEN DATASOURCE = 'CLOS' THEN (SELECT SUM(F.TAT_WORKING_HOUR) FROM F WHERE F.WI_NAME = WI_NAME AND F.WORKSTEP_CODE IN ('DetailDataEntry','DataInputerChecker','UnderwriterMaker','UnderwriterChecker','CreditApproval','CreditCommittee') AND F.APPROVAL_FLAG = 'First Approval') END</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>TSBD_G2</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Hồ sơ ≥2 tài sản bảo đảm</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Hồ sơ có từ 2 tài sản bảo đảm trở lên (RLOS-only, NULL nhánh CLOS). Dùng COUNT(*) thô (không phải COUNT DISTINCT — nguồn full-snapshot-mỗi-ngày), ngưỡng &gt;=2 theo ý nghĩa nghiệp vụ SRS</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F30" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT CASE WHEN COUNT(*) &gt;= 2 THEN 'YES' ELSE 'NO' END FROM H WHERE H.WI_NAME = A.WI_NAME AND H.DAYID = A.DAYID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="135" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>HS có từ 2 TSBĐ</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Hồ sơ có từ 2 tài sản bảo đảm trở lên (RLOS-only, NULL nhánh CLOS). COUNT(*) thô, ngưỡng &gt;=2. Lọc point-in-time trực tiếp theo DAYID=v_batch_date.</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE &lt;&gt; 'RLOS' THEN NULL ELSE (SELECT CASE WHEN COUNT(*) &gt;= 2 THEN 'YES' ELSE 'NO' END FROM H WHERE H.WI_NAME = WI_NAME AND H.DAYID = DAYID) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>INCOM_3</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Hồ sơ ≥3 nguồn thu</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Hồ sơ có từ 3 nguồn thu trở lên (RLOS-only, NULL nhánh CLOS)</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F31" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT CASE WHEN (CASE WHEN I.SALARYFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.CARFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.HOUSEFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.ENTERPRISSEFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.DIVINGFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.FAIMILYFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.NONLICFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.WAGESFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.PENSIONFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.OTHERFLAG = 'Yes' THEN 1 ELSE 0 END) &gt;= 3 THEN 'YES' ELSE 'NO' END FROM I WHERE I.APPLICATION_SK = A.APPLICATION_SK)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="75" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>HS có từ 3 nguồn thu</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>Hồ sơ có từ 3 nguồn thu trở lên (RLOS-only, NULL nhánh CLOS). SRS không định nghĩa cho CLOS. Nguồn là I (tầng STG_DTM), join qua APPLICATION_SK.</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE &lt;&gt; 'RLOS' THEN NULL ELSE (SELECT CASE WHEN (CASE WHEN I.SALARYFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.CARFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.HOUSEFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.ENTERPRISSEFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.DIVINGFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.FAIMILYFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.NONLICFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.WAGESFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.PENSIONFLAG = 'Yes' THEN 1 ELSE 0 END + CASE WHEN I.OTHERFLAG = 'Yes' THEN 1 ELSE 0 END) &gt;= 3 THEN 'YES' ELSE 'NO' END FROM I WHERE I.APPLICATION_SK = APPLICATION_SK) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>BUSINESS_INCOM</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Hồ sơ có nguồn thu kinh doanh</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>Hồ sơ có nguồn thu từ kinh doanh, không áp dụng SeAPro/SeALand (RLOS-only, NULL nhánh CLOS)</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F32" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT CASE WHEN (UPPER(I.PRODUCT_NAME) NOT LIKE '%SEAPRO%' AND UPPER(I.PRODUCT_NAME) NOT LIKE '%SEALAND%') AND (NVL(I.FAIMILYFLAG,'No') = 'Yes' OR NVL(I.ENTERPRISSEFLAG,'No') = 'Yes' OR NVL(I.NONLICFLAG,'No') = 'Yes') THEN 'YES' ELSE 'NO' END FROM I WHERE I.APPLICATION_SK = A.APPLICATION_SK)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>HS nguồn thu kinh doanh</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Hồ sơ có nguồn thu từ kinh doanh, không áp dụng SeAPro/SeALand (RLOS-only, NULL nhánh CLOS). Nguồn là I (tầng STG_DTM, bảng duy nhất có đủ 10 cột REPAYFLAGS), join qua APPLICATION_SK.</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE &lt;&gt; 'RLOS' THEN NULL ELSE (SELECT CASE WHEN (UPPER(I.PRODUCT_NAME) NOT LIKE '%SEAPRO%' AND UPPER(I.PRODUCT_NAME) NOT LIKE '%SEALAND%') AND (NVL(I.FAIMILYFLAG,'No') = 'Yes' OR NVL(I.ENTERPRISSEFLAG,'No') = 'Yes' OR NVL(I.NONLICFLAG,'No') = 'Yes') THEN 'YES' ELSE 'NO' END FROM I WHERE I.APPLICATION_SK = APPLICATION_SK) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="75" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>DEVIATION_G2</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Hồ sơ đúng 2 ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>Hồ sơ có đúng 2 ngoại lệ. COUNT(*) thô (nguồn full-snapshot-mỗi-ngày), lọc point-in-time theo DAYID=v_batch_date</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT CASE WHEN COUNT(*) = 2 THEN 'YES' ELSE 'NO' END FROM J WHERE J.WI_NAME = A.WI_NAME AND J.DAYID = A.DAYID)</t>
-        </is>
-      </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT CASE WHEN COUNT(*) = 2 THEN 'YES' ELSE 'NO' END FROM K WHERE K.WI_NAME = A.WI_NAME AND K.DAYID = A.DAYID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>HS có 2 ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>Hồ sơ có đúng 2 ngoại lệ. COUNT(*) thô. Lọc point-in-time trực tiếp theo DAYID=v_batch_date.</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE = 'RLOS' THEN (SELECT CASE WHEN COUNT(*) = 2 THEN 'YES' ELSE 'NO' END FROM K WHERE K.WI_NAME = WI_NAME AND K.DAYID = DAYID) WHEN DATASOURCE = 'CLOS' THEN (SELECT CASE WHEN COUNT(*) = 2 THEN 'YES' ELSE 'NO' END FROM J WHERE J.WI_NAME = WI_NAME AND J.DAYID = DAYID) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>DEVIATION_G3</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Hồ sơ ≥3 ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>HS có từ 3 ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
         <is>
           <t>Hồ sơ có từ 3 ngoại lệ trở lên. Cùng cách lọc DAYID point-in-time + COUNT(*) như DEVIATION_G2</t>
         </is>
       </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT CASE WHEN COUNT(*) &gt;= 3 THEN 'YES' ELSE 'NO' END FROM J WHERE J.WI_NAME = A.WI_NAME AND J.DAYID = A.DAYID)</t>
-        </is>
-      </c>
-      <c r="F34" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT CASE WHEN COUNT(*) &gt;= 3 THEN 'YES' ELSE 'NO' END FROM K WHERE K.WI_NAME = A.WI_NAME AND K.DAYID = A.DAYID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE = 'RLOS' THEN (SELECT CASE WHEN COUNT(*) &gt;= 3 THEN 'YES' ELSE 'NO' END FROM K WHERE K.WI_NAME = WI_NAME AND K.DAYID = DAYID) WHEN DATASOURCE = 'CLOS' THEN (SELECT CASE WHEN COUNT(*) &gt;= 3 THEN 'YES' ELSE 'NO' END FROM J WHERE J.WI_NAME = WI_NAME AND J.DAYID = DAYID) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>IS_TEST_ACCOUNT</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>Cờ tài khoản test</t>
         </is>
       </c>
-      <c r="D35" s="54" t="inlineStr">
-        <is>
-          <t>'Y' nếu hồ sơ có tồn tại (bất kỳ dòng lịch sử nào TÍNH ĐẾN v_batch_date) USERNAME thuộc 2 tài khoản test/kỹ thuật. AGG_LOS_KPI_YTD_DAILY loại các hồ sơ IS_TEST_ACCOUNT='Y' khỏi MỌI phép COUNT/SUM _DAY</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN EXISTS (SELECT 1 FROM L WHERE L.WI_NAME = A.WI_NAME AND L.USERNAME IN ('hanh.nh2','hai.bt2') AND L.ENTRYDATE &lt;= v_batch_date) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-      <c r="F35" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN EXISTS (SELECT 1 FROM M WHERE M.WI_NAME = A.WI_NAME AND M.USERNAME IN ('hanh.nh2','hai.bt2') AND M.ENTRYDATE &lt;= v_batch_date) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="D38" s="54" t="inlineStr">
+        <is>
+          <t>'Y' nếu hồ sơ có tồn tại (bất kỳ dòng lịch sử nào TÍNH ĐẾN v_batch_date) USERNAME thuộc 2 tài khoản test/kỹ thuật. EXISTS trên lịch sử hồ sơ CÓ ENTRYDATE&lt;=v_batch_date (point-in-time). AGG_LOS_KPI_YTD_DAILY loại các hồ sơ IS_TEST_ACCOUNT='Y' khỏi MỌI phép COUNT/SUM.</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN DATASOURCE = 'RLOS' THEN CASE WHEN EXISTS (SELECT 1 FROM M WHERE M.WI_NAME = WI_NAME AND M.USERNAME IN ('hanh.nh2','hai.bt2') AND M.ENTRYDATE &lt;= v_batch_date) THEN 'Y' ELSE 'N' END WHEN DATASOURCE = 'CLOS' THEN CASE WHEN EXISTS (SELECT 1 FROM L WHERE L.WI_NAME = WI_NAME AND L.USERNAME IN ('hanh.nh2','hai.bt2') AND L.ENTRYDATE &lt;= v_batch_date) THEN 'Y' ELSE 'N' END END</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_LINK_INFO</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>Thông tin liên kết hồ sơ</t>
         </is>
       </c>
-      <c r="D36" s="54" t="inlineStr">
-        <is>
-          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE (CLOS-only, RLOS luôn NULL). Dùng làm điều kiện lọc IS NOT NULL riêng cho SLHS_CLOS_DAY/SLGN_CLOS_DAY tại AGG_LOS_KPI_YTD_DAILY</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="D39" s="54" t="inlineStr">
+        <is>
+          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE (CLOS-only, RLOS luôn NULL). Dùng làm điều kiện lọc IS NOT NULL riêng cho SLHS_CLOS_DAY/SLGN_CLOS_DAY tại AGG_LOS_KPI_YTD_DAILY.</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>A.APPLICATION_LINK_INFO</t>
-        </is>
-      </c>
-      <c r="F36" s="31" t="inlineStr">
-        <is>
-          <t>NULL</t>
         </is>
       </c>
     </row>
